--- a/穆桂英挂帅_逐字声学数据_4.3.xlsx
+++ b/穆桂英挂帅_逐字声学数据_4.3.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>穆桂英挂帅.wav（44.1 kHz 立体声 16 bit，时长 111.93 s）</t>
+          <t>穆桂英挂帅修剪版.wav（44.1 kHz 立体声 16 bit，时长 72.54 s）= 穆桂英挂帅.wav 去掉开头 39.46 s</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>谐波分离（HPSS）后做 onset 起音点检测，共检出 82 个起音点；按唱词先后顺序取前 79 个与 79 个字一一对应，每字起始=该字起音点，结束=下一字起音点（末字结束取音频结尾 111.93 s）</t>
+          <t>原方法基于穆桂英挂帅.wav（111.93 s），本次按修剪版整体平移 −39.46 s（以两版共有字的拖腔起点标定，12 处地标中位偏差 −39.46 s）。修剪版起点=原版 39.46 s，落在第 3 段「冠」字拖腔中段：第 1 段全部、第 2 段全部与第 3 段「头戴金」在原版 39.46 s 前唱完，不在修剪版中（时间列已标注）；「冠」仅尾部 0.73 s 在修剪版内（起始记 0.00）；末字结束取修剪版音频末尾 72.54 s</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>是（2.28 s → 111.93 s，逐字首尾相接）</t>
+          <t>是（0.00 s → 72.54 s，逐字首尾相接）</t>
         </is>
       </c>
     </row>
@@ -759,11 +759,11 @@
           <t>66 (F#4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>88.63</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>89.28</v>
+      <c r="D2" s="6">
+        <v>49.17</v>
+      </c>
+      <c r="E2" s="6">
+        <v>49.82</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -785,11 +785,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>89.28</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>89.42</v>
+      <c r="D3" s="6">
+        <v>49.82</v>
+      </c>
+      <c r="E3" s="6">
+        <v>49.96</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>89.42</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>90.40000000000001</v>
+      <c r="D4" s="6">
+        <v>49.96</v>
+      </c>
+      <c r="E4" s="6">
+        <v>50.94</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -837,11 +837,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>91.72</v>
+      <c r="D5" s="6">
+        <v>50.94</v>
+      </c>
+      <c r="E5" s="6">
+        <v>52.26</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>91.72</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>93.37</v>
+      <c r="D2" s="6">
+        <v>52.26</v>
+      </c>
+      <c r="E2" s="6">
+        <v>53.91</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -943,11 +943,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>93.37</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>93.48</v>
+      <c r="D3" s="6">
+        <v>53.91</v>
+      </c>
+      <c r="E3" s="6">
+        <v>54.02</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -969,11 +969,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>93.48</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>94.2</v>
+      <c r="D4" s="6">
+        <v>54.02</v>
+      </c>
+      <c r="E4" s="6">
+        <v>54.74</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -995,11 +995,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>95.23</v>
+      <c r="D5" s="6">
+        <v>54.74</v>
+      </c>
+      <c r="E5" s="6">
+        <v>55.77</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -1021,11 +1021,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>95.23</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>95.92</v>
+      <c r="D6" s="6">
+        <v>55.77</v>
+      </c>
+      <c r="E6" s="6">
+        <v>56.46</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1047,11 +1047,11 @@
           <t>66 (F#4)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>95.92</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>97.04000000000001</v>
+      <c r="D7" s="6">
+        <v>56.46</v>
+      </c>
+      <c r="E7" s="6">
+        <v>57.58</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1073,11 +1073,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>97.04000000000001</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>98.01000000000001</v>
+      <c r="D8" s="6">
+        <v>57.58</v>
+      </c>
+      <c r="E8" s="6">
+        <v>58.55</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1099,11 +1099,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>98.01000000000001</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>98.36</v>
+      <c r="D9" s="6">
+        <v>58.55</v>
+      </c>
+      <c r="E9" s="6">
+        <v>58.90</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1125,11 +1125,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>98.36</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>99.2</v>
+      <c r="D10" s="6">
+        <v>58.90</v>
+      </c>
+      <c r="E10" s="6">
+        <v>59.74</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>102.19</v>
+      <c r="D11" s="6">
+        <v>59.74</v>
+      </c>
+      <c r="E11" s="6">
+        <v>62.73</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1177,11 +1177,11 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>102.19</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>102.45</v>
+      <c r="D12" s="6">
+        <v>62.73</v>
+      </c>
+      <c r="E12" s="6">
+        <v>62.99</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>102.45</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>111.93</v>
+      <c r="D13" s="6">
+        <v>62.99</v>
+      </c>
+      <c r="E13" s="6">
+        <v>72.54</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1283,11 +1283,15 @@
           <t>56 (G#3)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>3.2</v>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -1309,11 +1313,15 @@
           <t>57 (A3)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>3.44</v>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -1335,11 +1343,15 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>3.9</v>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -1361,11 +1373,15 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>4.27</v>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -1387,11 +1403,15 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>9.08</v>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1413,11 +1433,15 @@
           <t>51 (D#3)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>15.19</v>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1439,11 +1463,15 @@
           <t>57 (A3)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>17.09</v>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1465,11 +1493,15 @@
           <t>58 (A#3)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>17.23</v>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1491,11 +1523,15 @@
           <t>58 (A#3)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>17.23</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>20.94</v>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1517,11 +1553,15 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>21.76</v>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1597,11 +1637,15 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>21.76</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>23.68</v>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -1623,11 +1667,15 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>24.43</v>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -1649,11 +1697,15 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>25.43</v>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -1675,11 +1727,15 @@
           <t>65 (F4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>26.89</v>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -1701,11 +1757,15 @@
           <t>65 (F4)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>27.03</v>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1727,11 +1787,15 @@
           <t>56 (G#3)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>27.03</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>29.16</v>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1753,11 +1817,15 @@
           <t>51 (D#3)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>29.16</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>29.7</v>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1779,11 +1847,15 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>30.86</v>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1805,11 +1877,15 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>30.86</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>31.3</v>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1831,11 +1907,15 @@
           <t>55 (G3)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>31.76</v>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1857,11 +1937,15 @@
           <t>54 (F#3)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>32.88</v>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1937,11 +2021,15 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>34.27</v>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -1963,11 +2051,15 @@
           <t>65 (F4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>35.18</v>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -1989,11 +2081,15 @@
           <t>65 (F4)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>35.71</v>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>不在修剪版中</t>
+        </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2015,11 +2111,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>40.19</v>
+      <c r="D5" s="6">
+        <v>0.00</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.73</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2041,11 +2137,11 @@
           <t>54 (F#3)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>41.38</v>
+      <c r="D6" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.92</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2067,11 +2163,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>41.91</v>
+      <c r="D7" s="6">
+        <v>1.92</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.45</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -2093,11 +2189,11 @@
           <t>66 (F#4)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>43.44</v>
+      <c r="D8" s="6">
+        <v>2.45</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.98</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -2173,11 +2269,11 @@
           <t>63 (D#4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>44.35</v>
+      <c r="D2" s="6">
+        <v>3.98</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4.89</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2199,11 +2295,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>45.44</v>
+      <c r="D3" s="6">
+        <v>4.89</v>
+      </c>
+      <c r="E3" s="6">
+        <v>5.98</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2225,11 +2321,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>45.44</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>51.62</v>
+      <c r="D4" s="6">
+        <v>5.98</v>
+      </c>
+      <c r="E4" s="6">
+        <v>12.16</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2251,11 +2347,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>54.08</v>
+      <c r="D5" s="6">
+        <v>12.16</v>
+      </c>
+      <c r="E5" s="6">
+        <v>14.62</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2277,11 +2373,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>54.08</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>54.52</v>
+      <c r="D6" s="6">
+        <v>14.62</v>
+      </c>
+      <c r="E6" s="6">
+        <v>15.06</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2303,11 +2399,11 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>54.52</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>55.61</v>
+      <c r="D7" s="6">
+        <v>15.06</v>
+      </c>
+      <c r="E7" s="6">
+        <v>16.15</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -2329,11 +2425,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>56.35</v>
+      <c r="D8" s="6">
+        <v>16.15</v>
+      </c>
+      <c r="E8" s="6">
+        <v>16.89</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -2355,11 +2451,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>60.14</v>
+      <c r="D9" s="6">
+        <v>16.89</v>
+      </c>
+      <c r="E9" s="6">
+        <v>20.68</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -2381,11 +2477,11 @@
           <t>66 (F#4)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>62.11</v>
+      <c r="D10" s="6">
+        <v>20.68</v>
+      </c>
+      <c r="E10" s="6">
+        <v>22.65</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -2407,11 +2503,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>62.48</v>
+      <c r="D11" s="6">
+        <v>22.65</v>
+      </c>
+      <c r="E11" s="6">
+        <v>23.02</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -2433,11 +2529,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>62.48</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>64.48</v>
+      <c r="D12" s="6">
+        <v>23.02</v>
+      </c>
+      <c r="E12" s="6">
+        <v>25.02</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -2513,11 +2609,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>66.83</v>
+      <c r="D2" s="6">
+        <v>25.02</v>
+      </c>
+      <c r="E2" s="6">
+        <v>27.37</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2539,11 +2635,11 @@
           <t>65 (F4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>67.06</v>
+      <c r="D3" s="6">
+        <v>27.37</v>
+      </c>
+      <c r="E3" s="6">
+        <v>27.60</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2565,11 +2661,11 @@
           <t>66 (F#4)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>67.06</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>67.36</v>
+      <c r="D4" s="6">
+        <v>27.60</v>
+      </c>
+      <c r="E4" s="6">
+        <v>27.90</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2591,11 +2687,11 @@
           <t>63 (D#4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>67.8</v>
+      <c r="D5" s="6">
+        <v>27.90</v>
+      </c>
+      <c r="E5" s="6">
+        <v>28.34</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2617,11 +2713,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>68.61</v>
+      <c r="D6" s="6">
+        <v>28.34</v>
+      </c>
+      <c r="E6" s="6">
+        <v>29.15</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2643,11 +2739,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>68.61</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>69.45</v>
+      <c r="D7" s="6">
+        <v>29.15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>29.99</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -2723,11 +2819,11 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>69.45</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>69.98</v>
+      <c r="D2" s="6">
+        <v>29.99</v>
+      </c>
+      <c r="E2" s="6">
+        <v>30.52</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2749,11 +2845,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>69.98</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>70.23999999999999</v>
+      <c r="D3" s="6">
+        <v>30.52</v>
+      </c>
+      <c r="E3" s="6">
+        <v>30.78</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2775,11 +2871,11 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>70.87</v>
+      <c r="D4" s="6">
+        <v>30.78</v>
+      </c>
+      <c r="E4" s="6">
+        <v>31.41</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -2801,11 +2897,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>70.87</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>71.7</v>
+      <c r="D5" s="6">
+        <v>31.41</v>
+      </c>
+      <c r="E5" s="6">
+        <v>32.24</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -2827,11 +2923,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>72.14</v>
+      <c r="D6" s="6">
+        <v>32.24</v>
+      </c>
+      <c r="E6" s="6">
+        <v>32.68</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -2853,11 +2949,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>72.52</v>
+      <c r="D7" s="6">
+        <v>32.68</v>
+      </c>
+      <c r="E7" s="6">
+        <v>33.06</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -2879,11 +2975,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>74</v>
+      <c r="D8" s="6">
+        <v>33.06</v>
+      </c>
+      <c r="E8" s="6">
+        <v>34.54</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -2905,11 +3001,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>75.26000000000001</v>
+      <c r="D9" s="6">
+        <v>34.54</v>
+      </c>
+      <c r="E9" s="6">
+        <v>35.80</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -2985,11 +3081,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>75.26000000000001</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>76.02</v>
+      <c r="D2" s="6">
+        <v>35.80</v>
+      </c>
+      <c r="E2" s="6">
+        <v>36.56</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -3011,11 +3107,11 @@
           <t>67 (G4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>76.02</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>79.45999999999999</v>
+      <c r="D3" s="6">
+        <v>36.56</v>
+      </c>
+      <c r="E3" s="6">
+        <v>40.00</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3037,11 +3133,11 @@
           <t>54 (F#3)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>79.45999999999999</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>80.84999999999999</v>
+      <c r="D4" s="6">
+        <v>40.00</v>
+      </c>
+      <c r="E4" s="6">
+        <v>41.39</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3063,11 +3159,11 @@
           <t>54 (F#3)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>80.84999999999999</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>82.31</v>
+      <c r="D5" s="6">
+        <v>41.39</v>
+      </c>
+      <c r="E5" s="6">
+        <v>42.85</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -3089,11 +3185,11 @@
           <t>54 (F#3)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>82.31</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>84.66</v>
+      <c r="D6" s="6">
+        <v>42.85</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45.20</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -3169,11 +3265,11 @@
           <t>63 (D#4)</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>84.66</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>86.45</v>
+      <c r="D2" s="6">
+        <v>45.20</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46.99</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -3195,11 +3291,11 @@
           <t>60 (C4)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>86.45</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>87.84</v>
+      <c r="D3" s="6">
+        <v>46.99</v>
+      </c>
+      <c r="E3" s="6">
+        <v>48.38</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3221,11 +3317,11 @@
           <t>59 (B3)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>87.84</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>88.17</v>
+      <c r="D4" s="6">
+        <v>48.38</v>
+      </c>
+      <c r="E4" s="6">
+        <v>48.71</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -3247,11 +3343,11 @@
           <t>61 (C#4)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>88.17</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>88.31</v>
+      <c r="D5" s="6">
+        <v>48.71</v>
+      </c>
+      <c r="E5" s="6">
+        <v>48.85</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -3273,11 +3369,11 @@
           <t>62 (D4)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>88.31</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>88.63</v>
+      <c r="D6" s="6">
+        <v>48.85</v>
+      </c>
+      <c r="E6" s="6">
+        <v>49.17</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
